--- a/artfynd/A 59431-2025 artfynd.xlsx
+++ b/artfynd/A 59431-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130091786</v>
       </c>
       <c r="B2" t="n">
-        <v>96950</v>
+        <v>96952</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59431-2025 artfynd.xlsx
+++ b/artfynd/A 59431-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130091786</v>
       </c>
       <c r="B2" t="n">
-        <v>96952</v>
+        <v>97039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130091777</v>
       </c>
       <c r="B3" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59431-2025 artfynd.xlsx
+++ b/artfynd/A 59431-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130091786</v>
       </c>
       <c r="B2" t="n">
-        <v>97039</v>
+        <v>97231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130091777</v>
+        <v>130091792</v>
       </c>
       <c r="B3" t="n">
-        <v>78937</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557309</v>
+        <v>557214</v>
       </c>
       <c r="R3" t="n">
-        <v>6823075</v>
+        <v>6823086</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,10 +871,111 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>Jenss Hansen, Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130091777</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Björnmyra NO, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>557309</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6823075</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Undersvik</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Jenss Hansen</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59431-2025 artfynd.xlsx
+++ b/artfynd/A 59431-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091786</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091792</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,8 +991,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091777</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>